--- a/QCM1_1_PHY.xlsx
+++ b/QCM1_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA42396-C7F4-4DB9-907E-18BA88A04E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB827AA-7671-44A9-B968-6DAD24D62B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,22 +255,22 @@
     <t>L'abscisse du centre d'inertie G lorsque $E_c = E_{pe}$ vaut :</t>
   </si>
   <si>
-    <t>$60 \, \mu \mathrm{C} ; $\quad$ 2,3 \text{ s}$</t>
-  </si>
-  <si>
-    <t>$6 \, \mu \mathrm{C} ; $\quad$ 2,3 \text{ s}$</t>
-  </si>
-  <si>
-    <t>$60 \, \mu \mathrm{C} ; $\quad$ 4,6 \text{ s}$</t>
-  </si>
-  <si>
-    <t>$60 \, \mu \mathrm{C} ; $\quad$ 1 \text{ s}$</t>
-  </si>
-  <si>
-    <t>$6 \, \mu \mathrm{C} ; $\quad$ 1 \text{ s}$</t>
-  </si>
-  <si>
-    <t>On charge un condensateur de capacité $C = 10 \mu F}$ avec un générateur de tension idéale continue $U_0 = 6\text{ V}$ à travers une résistance $R = 0,1 \text{ M}\Omega$. La valeur de $Q_{max}$ et le temps nécessaire pour que la charge atteigne 90% de sa valeur maximale sont (On donne $\ln(10) \approx 2,3$) :</t>
+    <t>$60 \, \mu \mathrm{C} ;$ $\quad$ $2,3 \text{ s}$</t>
+  </si>
+  <si>
+    <t>$6 \, \mu \mathrm{C} ;$ $\quad$ $2,3 \text{ s}$</t>
+  </si>
+  <si>
+    <t>$60 \, \mu \mathrm{C} ;$ $\quad$ $4,6 \text{ s}$</t>
+  </si>
+  <si>
+    <t>$60 \, \mu \mathrm{C} ;$ $\quad$ $1 \text{ s}$</t>
+  </si>
+  <si>
+    <t>$6 \, \mu \mathrm{C} ; \quad 1 \text{ s}$</t>
+  </si>
+  <si>
+    <t>On charge un condensateur de capacité $C = 10 \mu \mathrm{F}$ avec un générateur de tension idéale continue $U_0 = 6\text{ V}$ à travers une résistance $R = 0,1 \text{ M}\Omega$. La valeur de $Q_{max}$ et le temps nécessaire pour que la charge atteigne 90% de sa valeur maximale sont (On donne $\ln(10) \approx 2,3$) :</t>
   </si>
 </sst>
 </file>

--- a/QCM1_1_PHY.xlsx
+++ b/QCM1_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB827AA-7671-44A9-B968-6DAD24D62B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B608B02B-5477-4560-A570-E5721B02160D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
   <si>
     <t>Question</t>
   </si>
@@ -790,9 +790,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="C2" s="6"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -894,9 +892,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="C6" s="6"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
@@ -1027,9 +1023,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="C11" s="6"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -1102,9 +1096,7 @@
         <v>58</v>
       </c>
       <c r="B14" s="12"/>
-      <c r="C14" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="C14" s="6"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
